--- a/Non Veg Pizza Price Details.xlsx
+++ b/Non Veg Pizza Price Details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Shamshad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15129D0-43F0-4269-8F41-9CBFEF2A777B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9E40FC-A407-442E-9FBF-71443A431412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="196">
   <si>
     <t>Restaurant</t>
   </si>
@@ -425,13 +425,208 @@
     <t>   Upto ₹ 500</t>
   </si>
   <si>
+    <t xml:space="preserve">Onesta </t>
+  </si>
+  <si>
+    <t>₹ 799.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                     ₹500 </t>
+  </si>
+  <si>
+    <t>Pizza Palace</t>
+  </si>
+  <si>
+    <t>More Pizza</t>
+  </si>
+  <si>
+    <t>Pizza Da Dhaba</t>
+  </si>
+  <si>
+    <t>Cafe Zuppa</t>
+  </si>
+  <si>
+    <t>Intalia</t>
+  </si>
+  <si>
+    <t>Mahek Pizza</t>
+  </si>
+  <si>
+    <t>The Hungers Zone</t>
+  </si>
+  <si>
+    <t>Calvin's</t>
+  </si>
+  <si>
+    <t>Pizza Paradise</t>
+  </si>
+  <si>
+    <t>Bangalore Pizza &amp; Pulse Juice Bar</t>
+  </si>
+  <si>
+    <t>Pizza On The Way</t>
+  </si>
+  <si>
+    <t>Orlando's Pizzeria</t>
+  </si>
+  <si>
+    <t>Juice Fresco &amp; Pizza</t>
+  </si>
+  <si>
+    <t>Agastya Suites, 116, 8th Main Road, Next to M.K.Ahmed Retail, 4th Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>Hongasandra, 1st Main Road, Bommanahalli, Bangalore</t>
+  </si>
+  <si>
+    <t>Ground Floor, 21, Krishnama Raju Layout, Near Oracle Dorasani Palya, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>Beside Radiant Shine Apartment, Akshaya Nagar, Yellanahalli, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>81/3/4, 5th Cross, Opposite Royal Meenakshi Mall, Hulimavu, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>24th Main, 5th Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>779, 16th Main, 14th Cross, Near Mico Layout Police Station, 2nd Stage, BTM, Bangalore</t>
+  </si>
+  <si>
+    <t>Bommanahalli</t>
+  </si>
+  <si>
+    <t>₹450 </t>
+  </si>
+  <si>
+    <t> ₹400</t>
+  </si>
+  <si>
+    <t> ₹1000</t>
+  </si>
+  <si>
+    <t>₹1–200</t>
+  </si>
+  <si>
+    <t>₹300 </t>
+  </si>
+  <si>
+    <t>Near Reliance Mart, Shabari Complex, Arakere Mico Layout, Off B G Road, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>7 &amp; 8, Kodichikkanahalli Main Road, Bommanahalli, Bangalore</t>
+  </si>
+  <si>
+    <t>206, 30th B Main Road, 6th Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>4th Floor, Gopalan Innovation Mall, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>1274, 2nd Cross, 1st Block, Opposite RMR Park, Devarachikkanahalli Road, BTM 4th Stage, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>1, Pai Layout, Hulimavu Main Road, Bannerghatta Road, Bangalore, Bengaluru</t>
+  </si>
+  <si>
+    <t>47/1, 9th Main, 1st Cross, 3rd Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>Eden Park7, 8 Doresani Palya, Near Kalyani Magnum, Opposite Oracle, 5th Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>26/2, Dodda Kammanahalli, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>18, 7th Main Road, NS Palya, Stage 2, BTM, Bangalore</t>
+  </si>
+  <si>
+    <t>Flow - Terrace Bar &amp; Grill</t>
+  </si>
+  <si>
+    <t>Ishta Cafe</t>
+  </si>
+  <si>
+    <t>Insta Cafe</t>
+  </si>
+  <si>
+    <t>67, 15th Cross, 3rd Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t> ₹500</t>
+  </si>
+  <si>
+    <t>₹250 </t>
+  </si>
+  <si>
+    <t>Below ₹500</t>
+  </si>
+  <si>
+    <t> ₹200 </t>
+  </si>
+  <si>
+    <t>₹400 </t>
+  </si>
+  <si>
+    <t>Spar Refresh</t>
+  </si>
+  <si>
+    <t>Brahma Brews</t>
+  </si>
+  <si>
+    <t>Enerjuvate Studio &amp; Cafe</t>
+  </si>
+  <si>
+    <t>The Airos</t>
+  </si>
+  <si>
+    <t>Bread and Circus</t>
+  </si>
+  <si>
+    <t>Java City</t>
+  </si>
+  <si>
+    <t>Shanti Nagar</t>
+  </si>
+  <si>
+    <t>10, 1st Floor, Opposite Royal Meenakshi Mall, Hulimavu, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>Ground Floor,Vega City Mall, Bannerghatta Road, Bengaluru</t>
+  </si>
+  <si>
+    <t>8, Arikere Gate, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>31, 4th Cross Road, Panduranga Nagar, Bannerghatta Road, Bangalore</t>
+  </si>
+  <si>
+    <t>24th Main, 7th Phase, Opposite Brigade Palm Springs, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>90/66, 1st Floor, Gandhi Bazar Main Road, Basavanagudi, Bangalore</t>
+  </si>
+  <si>
+    <t>Shop 547, 32nd C Cross, 9th Main, 4th Block, Jayanagar, Bangalore</t>
+  </si>
+  <si>
+    <t>Lal Bagh Main Road, Sampangi Rama Nagar, Near Shanti Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>539, 10th Main, 5th Block, Jayanagar, Bangalore</t>
+  </si>
+  <si>
+    <t> ₹200</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">                   </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="12"/>
         <color rgb="FF767676"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -440,7 +635,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="8"/>
+        <sz val="12"/>
         <color rgb="FF474747"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -449,13 +644,28 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Onesta </t>
-  </si>
-  <si>
-    <t>₹ 799.00 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                     ₹500 </t>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>₹329 to ₹389</t>
+    </r>
+  </si>
+  <si>
+    <t> ₹1000 </t>
+  </si>
+  <si>
+    <t> ₹750</t>
+  </si>
+  <si>
+    <t> ₹300</t>
   </si>
 </sst>
 </file>
@@ -466,7 +676,7 @@
     <numFmt numFmtId="6" formatCode="&quot;₹&quot;\ #,##0;[Red]&quot;₹&quot;\ \-#,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,38 +748,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF767676"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF5E5E5E"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF474747"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF4D5156"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF001D35"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -579,6 +770,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9FBFD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,53 +816,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="6" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -946,581 +1140,581 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="32.88671875" style="14" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="14" customWidth="1"/>
-    <col min="4" max="4" width="39.44140625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="14" style="14" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="32.21875" style="14" customWidth="1"/>
-    <col min="9" max="9" width="103.21875" style="14" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="14"/>
+    <col min="1" max="1" width="7.77734375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="39.44140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="14" style="8" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="32.21875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="112.88671875" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A2" s="15">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="10">
         <v>379</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="10">
         <v>849</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="10">
         <v>700</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A3" s="15">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="10">
         <v>339</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="10">
         <v>650</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="10">
         <v>300</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
     </row>
     <row r="4" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A4" s="15">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="10">
         <v>200</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="10">
         <v>500</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="10">
         <v>350</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A5" s="15">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="10">
         <v>189</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="10">
         <v>339</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="10">
         <v>249</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="10">
         <v>459</v>
       </c>
-      <c r="H6" s="17"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A7" s="15">
+      <c r="A7" s="9">
         <v>5</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="C7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="8">
         <v>99</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="14">
+      <c r="F7" s="10"/>
+      <c r="G7" s="8">
         <v>450</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A8" s="15">
+      <c r="A8" s="9">
         <v>6</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="C8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="H8" s="17" t="s">
+      <c r="F8" s="10"/>
+      <c r="H8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A9" s="15">
+      <c r="A9" s="9">
         <v>7</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="C9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A10" s="15">
+      <c r="A10" s="9">
         <v>8</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="20">
+      <c r="C10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="5">
         <v>400</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A11" s="15">
+      <c r="A11" s="9">
         <v>9</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="16">
+      <c r="C11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="10">
         <v>400</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A12" s="15">
+      <c r="A12" s="9">
         <v>10</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="21">
+      <c r="C12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="14">
         <v>250</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A13" s="15">
+      <c r="A13" s="9">
         <v>11</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="14">
+      <c r="C13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="8">
         <v>300</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="9" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A14" s="15">
+      <c r="A14" s="9">
         <v>12</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="22" t="s">
+      <c r="C14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A15" s="15">
+      <c r="A15" s="9">
         <v>13</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="16" t="s">
+      <c r="C15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.2" thickBot="1">
-      <c r="A16" s="15">
+      <c r="A16" s="9">
         <v>14</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="20" t="s">
+      <c r="C16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A17" s="15">
+      <c r="A17" s="9">
         <v>15</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="22" t="s">
+      <c r="C17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="5">
         <v>700</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A18" s="15">
+      <c r="A18" s="9">
         <v>16</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="23">
+      <c r="C18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="15">
         <v>400</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="15">
         <v>600</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A19" s="15">
+      <c r="A19" s="9">
         <v>17</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="21">
+      <c r="C19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="14">
         <v>500</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="14">
         <v>1000</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="9" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A20" s="15">
+      <c r="A20" s="9">
         <v>18</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="23">
+      <c r="C20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="15">
         <v>400</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="15">
         <v>600</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A21" s="15">
-        <v>19</v>
-      </c>
-      <c r="B21" s="15" t="s">
+      <c r="A21" s="9">
+        <v>19</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" s="24">
+      <c r="C21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="16">
         <v>400</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A22" s="15">
+      <c r="A22" s="9">
         <v>20</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="25" t="s">
+      <c r="C22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="3">
         <v>1000</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A23" s="15">
+      <c r="A23" s="9">
         <v>21</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="14" t="s">
+      <c r="C23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E23" s="4" t="s">
@@ -1532,93 +1726,93 @@
       <c r="G23" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="H23" s="15" t="s">
+      <c r="H23" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" s="9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A24" s="15">
+      <c r="A24" s="9">
         <v>22</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G24" s="24">
+      <c r="C24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="16">
         <v>850</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A25" s="15">
+      <c r="A25" s="9">
         <v>23</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="14" t="s">
+      <c r="C25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A26" s="15">
+      <c r="A26" s="9">
         <v>24</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="14" t="s">
+      <c r="C26" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A27" s="14">
+      <c r="A27" s="8">
         <v>25</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="14" t="s">
+      <c r="C27" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E27" s="3">
@@ -1627,73 +1821,73 @@
       <c r="F27" s="3">
         <v>1000</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="H27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A28" s="14">
+      <c r="A28" s="8">
         <v>26</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="14" t="s">
+      <c r="C28" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G28" s="2">
         <v>200</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A29" s="14">
+      <c r="A29" s="8">
         <v>27</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="25" t="s">
+      <c r="C29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="14" t="s">
         <v>115</v>
       </c>
       <c r="F29" s="3">
         <v>1000</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="H29" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="I29" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A30" s="14">
+      <c r="A30" s="8">
         <v>28</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="14" t="s">
+      <c r="C30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E30" s="3">
@@ -1702,116 +1896,116 @@
       <c r="F30" s="3">
         <v>1000</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A31" s="14">
+      <c r="A31" s="8">
         <v>29</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C31" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="25" t="s">
+      <c r="C31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="14" t="s">
         <v>117</v>
       </c>
       <c r="F31" s="3">
         <v>1000</v>
       </c>
-      <c r="H31" s="15" t="s">
+      <c r="H31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="9" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A32" s="14">
+      <c r="A32" s="8">
         <v>30</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E32" s="26">
+      <c r="C32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="17">
         <v>200</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="H32" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A33" s="14">
+      <c r="A33" s="8">
         <v>31</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="14" t="s">
+      <c r="C33" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G33" s="1">
         <v>600</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="9" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A34" s="14">
+      <c r="A34" s="8">
         <v>32</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" s="15" t="s">
+      <c r="C34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A35" s="14">
+      <c r="A35" s="8">
         <v>33</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="14" t="s">
+      <c r="C35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E35" s="3">
@@ -1820,411 +2014,1594 @@
       <c r="F35" s="3">
         <v>1000</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="H35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="9" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A36" s="14">
+      <c r="A36" s="8">
         <v>34</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H36" s="15" t="s">
+      <c r="C36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A37" s="14">
+      <c r="A37" s="8">
         <v>35</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="14" t="s">
+      <c r="C37" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="H37" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A38" s="14">
+      <c r="A38" s="8">
         <v>36</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="14" t="s">
+      <c r="C38" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H38" s="15" t="s">
+      <c r="H38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="I38" s="9" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A39" s="14">
+      <c r="A39" s="8">
         <v>37</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="14" t="s">
+      <c r="C39" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>73</v>
       </c>
       <c r="G39" s="1">
         <v>1800</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H39" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="9" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A40" s="14">
+      <c r="A40" s="8">
         <v>38</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="27">
+      <c r="B40" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="18">
         <v>500</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="18">
         <v>1000</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H40" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A41" s="14">
+      <c r="A41" s="8">
         <v>39</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="H41" s="15" t="s">
+      <c r="C41" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="9" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A42" s="14">
+      <c r="A42" s="8">
         <v>40</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="14" t="s">
+      <c r="C42" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A43" s="14">
+      <c r="A43" s="8">
         <v>41</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G43" s="6">
+      <c r="C43" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G43" s="2">
         <v>300</v>
       </c>
-      <c r="H43" s="15" t="s">
+      <c r="H43" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A44" s="14">
+      <c r="A44" s="8">
         <v>42</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G44" s="28">
+      <c r="C44" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" s="19">
         <v>550</v>
       </c>
-      <c r="H44" s="15" t="s">
+      <c r="H44" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="I44" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A45" s="14">
+      <c r="A45" s="8">
         <v>43</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G45" s="8" t="s">
+      <c r="C45" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="47.4" thickBot="1">
+      <c r="A46" s="8">
+        <v>44</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A47" s="8">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="H45" s="15" t="s">
+      <c r="F47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="47.4" thickBot="1">
+      <c r="A48" s="8">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="16">
+        <v>99</v>
+      </c>
+      <c r="F48" s="16">
+        <v>149</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A49" s="8">
+        <v>47</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" s="20">
+        <v>200</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A50" s="8">
+        <v>48</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G50" s="20">
+        <v>1000</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A51" s="8">
+        <v>49</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G51" s="16">
+        <v>400</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I45" s="15" t="s">
+      <c r="I51" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A52" s="8">
+        <v>50</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A53" s="8">
+        <v>51</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G53" s="17">
+        <v>200</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A54" s="8">
+        <v>52</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="20">
+        <v>250</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A55" s="8">
+        <v>53</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="G55" s="20">
+        <v>1500</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A56" s="8">
+        <v>54</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56" s="17">
+        <v>200</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A57" s="8">
+        <v>55</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A58" s="8">
+        <v>56</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A59" s="8">
+        <v>56</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A60" s="8">
+        <v>57</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A61" s="8">
+        <v>58</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A62" s="8">
+        <v>59</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A63" s="8">
+        <v>60</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G63" s="17">
+        <v>200</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A64" s="8">
+        <v>61</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A65" s="8">
+        <v>62</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" s="3">
+        <v>500</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="31.8" thickBot="1">
+      <c r="A66" s="8">
+        <v>63</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G66" s="17">
+        <v>200</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A67" s="8">
+        <v>64</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A68" s="8">
+        <v>65</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A69" s="8">
+        <v>66</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E69" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F69" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A70" s="8">
+        <v>67</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G70" s="2">
+        <v>200</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A71" s="8">
+        <v>68</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A72" s="8">
+        <v>69</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A73" s="8">
+        <v>70</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A74" s="8">
+        <v>71</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A75" s="8">
+        <v>72</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A76" s="4">
+        <v>73</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G76" s="20">
+        <v>200</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="31.8" thickBot="1">
+      <c r="A77" s="8">
+        <v>74</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G77" s="17">
+        <v>200</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A78" s="8">
+        <v>75</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G78" s="2">
+        <v>300</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A79" s="8">
+        <v>76</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G79" s="2">
+        <v>200</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A80" s="8">
+        <v>77</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G80" s="2">
+        <v>250</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A81" s="8">
+        <v>78</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A82" s="8">
+        <v>79</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F82" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A83" s="8">
+        <v>80</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G83" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I83" s="9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="47.4" thickBot="1">
-      <c r="A46" s="14">
+    <row r="84" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A84" s="8">
+        <v>81</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="F84" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A85" s="8">
+        <v>82</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A86" s="8">
+        <v>83</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F86" s="2">
+        <v>800</v>
+      </c>
+      <c r="G86" s="1">
+        <v>200</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A87" s="8">
+        <v>84</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G87" s="17">
+        <v>200</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A88" s="8">
+        <v>85</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G88" s="17">
+        <v>200</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A89" s="8">
+        <v>86</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F89" s="2">
+        <v>2500</v>
+      </c>
+      <c r="G89" s="2">
+        <v>750</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A90" s="8">
+        <v>87</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G90" s="3">
+        <v>600</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A91" s="8">
+        <v>89</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G91" s="23">
+        <v>399</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A92" s="8">
+        <v>90</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G92" s="3">
+        <v>600</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A93" s="8">
+        <v>91</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G93" s="17">
+        <v>400</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A94" s="8">
+        <v>92</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G94" s="2">
+        <v>550</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A95" s="8">
+        <v>93</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G95" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A96" s="8">
+        <v>94</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A97" s="8">
+        <v>95</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E97" s="3">
+        <v>500</v>
+      </c>
+      <c r="F97" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A98" s="8">
+        <v>96</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G98" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I98" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A47" s="14">
+    </row>
+    <row r="99" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A99" s="8">
+        <v>97</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G99" s="23">
+        <v>200</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A100" s="8">
+        <v>98</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G100" s="3">
+        <v>200</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A101" s="8">
+        <v>99</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I101" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F47" s="7">
-        <v>1000</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="47.4" thickBot="1">
-      <c r="A48" s="14">
-        <v>46</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E48" s="11">
-        <v>99</v>
-      </c>
-      <c r="F48" s="11">
-        <v>149</v>
-      </c>
-      <c r="H48" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A49" s="14">
-        <v>47</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G49" s="29">
-        <v>200</v>
-      </c>
-      <c r="H49" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A50" s="14">
-        <v>48</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G50" s="29">
-        <v>1000</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="I50" s="15" t="s">
+    </row>
+    <row r="102" spans="1:9" ht="16.2" thickBot="1">
+      <c r="A102" s="8">
         <v>100</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A51" s="14">
-        <v>49</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G51" s="11">
+      <c r="B102" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="H51" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A52" s="14">
-        <v>50</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F52" s="7">
-        <v>1000</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>102</v>
+      <c r="H102" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/Non Veg Pizza Price Details.xlsx
+++ b/Non Veg Pizza Price Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Shamshad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9E40FC-A407-442E-9FBF-71443A431412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D9C971-CFD2-4059-8DEA-89CE0A4AD291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="236">
   <si>
     <t>Restaurant</t>
   </si>
@@ -667,6 +667,137 @@
   <si>
     <t> ₹300</t>
   </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>LIT Gastro Pub</t>
+  </si>
+  <si>
+    <t>Grillopia</t>
+  </si>
+  <si>
+    <t>Salut</t>
+  </si>
+  <si>
+    <t>Ragoo's</t>
+  </si>
+  <si>
+    <t>Mockaholic Restro Beer Cafe</t>
+  </si>
+  <si>
+    <t>1441 Pizzeria</t>
+  </si>
+  <si>
+    <t>SMM Pizzeria</t>
+  </si>
+  <si>
+    <t>Garage Pizza</t>
+  </si>
+  <si>
+    <t>'RATED\n Very bad no proper seats poor taste and serving no chance of adding toppings only 1 menu card vry vry bad taste so small place and poor serving')</t>
+  </si>
+  <si>
+    <t>Once Upon a Rooftop</t>
+  </si>
+  <si>
+    <t>Sarvam's</t>
+  </si>
+  <si>
+    <t>Tasty Bites</t>
+  </si>
+  <si>
+    <t>Little Italy</t>
+  </si>
+  <si>
+    <t>Chef Baker's</t>
+  </si>
+  <si>
+    <t>Stoner</t>
+  </si>
+  <si>
+    <t>Eating Love</t>
+  </si>
+  <si>
+    <t>Imperio Cafe</t>
+  </si>
+  <si>
+    <t>NY Pizza And Waffles</t>
+  </si>
+  <si>
+    <t>233, 4th Floor, 40th cross, 9th Main Road, 5th Block, Jayanagar, Bangalore</t>
+  </si>
+  <si>
+    <t>Wilson Garden</t>
+  </si>
+  <si>
+    <t>280-3, 9th Cross, Opposite Post Office, Wilson Garden, Bangalore</t>
+  </si>
+  <si>
+    <t>5, Krishna Nagar, Next To Royal Endfield Showroom, Hosur Road, BTM, Bangalore</t>
+  </si>
+  <si>
+    <t>1107, R.V.Dental College Road, 24th Main, 1st Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>1105, Archana Arcade, 24th Main, 1st Phase, JP Nagar, Bangalore</t>
+  </si>
+  <si>
+    <t>83/3, Pride Plaza, 5th Main, Chamrajpet, Basavanagudi, Bangalore</t>
+  </si>
+  <si>
+    <t>1/1,5th Cross Rd, Shankarapura, Bengaluru, Karnataka 560004, India</t>
+  </si>
+  <si>
+    <t>38, Ground Floor, Bull Temple Road, Basavanagudi, Bangalore</t>
+  </si>
+  <si>
+    <t>19, Mobas Towers, Bull Temple Road, Basavanagudi, Bangalore</t>
+  </si>
+  <si>
+    <t>pizza boxes were thrown all over on the tables... Very very very unhygienic.... I would say it's better to stay hungry or it's better to control our temptation rather entering to such dirty place like Pizza Hut ( Basvangudi franchises )...\nI had order Potatoes poppers n garlic bread both was worst in taste ..potatoes poppers was not fried properly... Garlic bread was stale.... Really Waste of time n money..."")</t>
+  </si>
+  <si>
+    <t>('Rated 1.0'</t>
+  </si>
+  <si>
+    <t>₹1–200 </t>
+  </si>
+  <si>
+    <t>₹1,000 </t>
+  </si>
+  <si>
+    <t>Rs.800</t>
+  </si>
+  <si>
+    <t>Rs.500</t>
+  </si>
+  <si>
+    <t> ₹400 </t>
+  </si>
+  <si>
+    <t> ₹ 250</t>
+  </si>
+  <si>
+    <t>₹200 </t>
+  </si>
+  <si>
+    <t> Rs. 339</t>
+  </si>
+  <si>
+    <r>
+      <t>399.00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF474747"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -676,7 +807,7 @@
     <numFmt numFmtId="6" formatCode="&quot;₹&quot;\ #,##0;[Red]&quot;₹&quot;\ \-#,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -753,12 +884,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF001D35"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -816,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -858,8 +983,13 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1140,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:AH154"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="8" customWidth="1"/>
@@ -1152,7 +1282,8 @@
     <col min="7" max="7" width="13.33203125" style="8" customWidth="1"/>
     <col min="8" max="8" width="32.21875" style="8" customWidth="1"/>
     <col min="9" max="9" width="112.88671875" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="8"/>
+    <col min="10" max="11" width="12.88671875" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1">
@@ -1182,6 +1313,9 @@
       </c>
       <c r="I1" s="7" t="s">
         <v>24</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.2" thickBot="1">
@@ -3338,7 +3472,7 @@
       <c r="D91" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G91" s="23">
+      <c r="G91" s="20">
         <v>399</v>
       </c>
       <c r="H91" s="9" t="s">
@@ -3430,7 +3564,7 @@
       <c r="D95" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G95" s="24" t="s">
+      <c r="G95" s="10" t="s">
         <v>194</v>
       </c>
       <c r="H95" s="9" t="s">
@@ -3463,7 +3597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="16.2" thickBot="1">
+    <row r="97" spans="1:34" ht="16.2" thickBot="1">
       <c r="A97" s="8">
         <v>95</v>
       </c>
@@ -3489,7 +3623,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="16.2" thickBot="1">
+    <row r="98" spans="1:34" ht="16.2" thickBot="1">
       <c r="A98" s="8">
         <v>96</v>
       </c>
@@ -3512,7 +3646,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="16.2" thickBot="1">
+    <row r="99" spans="1:34" ht="16.2" thickBot="1">
       <c r="A99" s="8">
         <v>97</v>
       </c>
@@ -3525,7 +3659,7 @@
       <c r="D99" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G99" s="23">
+      <c r="G99" s="20">
         <v>200</v>
       </c>
       <c r="H99" s="9" t="s">
@@ -3535,7 +3669,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="16.2" thickBot="1">
+    <row r="100" spans="1:34" ht="16.2" thickBot="1">
       <c r="A100" s="8">
         <v>98</v>
       </c>
@@ -3558,7 +3692,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="16.2" thickBot="1">
+    <row r="101" spans="1:34" ht="16.2" thickBot="1">
       <c r="A101" s="8">
         <v>99</v>
       </c>
@@ -3581,7 +3715,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="16.2" thickBot="1">
+    <row r="102" spans="1:34" ht="16.2" thickBot="1">
       <c r="A102" s="8">
         <v>100</v>
       </c>
@@ -3603,6 +3737,2205 @@
       <c r="I102" s="9" t="s">
         <v>189</v>
       </c>
+    </row>
+    <row r="103" spans="1:34" ht="17.399999999999999" customHeight="1" thickBot="1">
+      <c r="A103" s="8">
+        <v>101</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J103" s="23"/>
+      <c r="K103" s="9"/>
+      <c r="L103" s="9"/>
+      <c r="M103" s="9"/>
+      <c r="N103" s="9"/>
+      <c r="O103" s="9"/>
+      <c r="P103" s="9"/>
+      <c r="Q103" s="9"/>
+      <c r="R103" s="9"/>
+      <c r="S103" s="9"/>
+      <c r="T103" s="9"/>
+      <c r="U103" s="9"/>
+      <c r="V103" s="9"/>
+      <c r="W103" s="9"/>
+      <c r="X103" s="9"/>
+      <c r="Y103" s="9"/>
+      <c r="Z103" s="9"/>
+      <c r="AA103" s="9"/>
+      <c r="AB103" s="9"/>
+      <c r="AC103" s="9"/>
+      <c r="AD103" s="9"/>
+      <c r="AE103" s="9"/>
+      <c r="AF103" s="9"/>
+      <c r="AG103" s="9"/>
+      <c r="AH103" s="9"/>
+    </row>
+    <row r="104" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A104" s="8">
+        <v>102</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G104" s="16">
+        <v>900</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="J104" s="23"/>
+      <c r="K104" s="9"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="9"/>
+      <c r="N104" s="9"/>
+      <c r="O104" s="9"/>
+      <c r="P104" s="9"/>
+      <c r="Q104" s="9"/>
+      <c r="R104" s="9"/>
+      <c r="S104" s="9"/>
+      <c r="T104" s="9"/>
+      <c r="U104" s="9"/>
+      <c r="V104" s="9"/>
+      <c r="W104" s="9"/>
+      <c r="X104" s="9"/>
+      <c r="Y104" s="9"/>
+      <c r="Z104" s="9"/>
+      <c r="AA104" s="9"/>
+      <c r="AB104" s="9"/>
+      <c r="AC104" s="9"/>
+      <c r="AD104" s="9"/>
+      <c r="AE104" s="9"/>
+      <c r="AF104" s="9"/>
+      <c r="AG104" s="9"/>
+      <c r="AH104" s="9"/>
+    </row>
+    <row r="105" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A105" s="8">
+        <v>103</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G105" s="3">
+        <v>200</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="I105" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="J105" s="23"/>
+      <c r="K105" s="9"/>
+      <c r="L105" s="9"/>
+      <c r="M105" s="9"/>
+      <c r="N105" s="9"/>
+      <c r="O105" s="9"/>
+      <c r="P105" s="9"/>
+      <c r="Q105" s="9"/>
+      <c r="R105" s="9"/>
+      <c r="S105" s="9"/>
+      <c r="T105" s="9"/>
+      <c r="U105" s="9"/>
+      <c r="V105" s="9"/>
+      <c r="W105" s="9"/>
+      <c r="X105" s="9"/>
+      <c r="Y105" s="9"/>
+      <c r="Z105" s="9"/>
+      <c r="AA105" s="9"/>
+      <c r="AB105" s="9"/>
+      <c r="AC105" s="9"/>
+      <c r="AD105" s="9"/>
+      <c r="AE105" s="9"/>
+      <c r="AF105" s="9"/>
+      <c r="AG105" s="9"/>
+      <c r="AH105" s="9"/>
+    </row>
+    <row r="106" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A106" s="8">
+        <v>104</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="J106" s="23"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="9"/>
+      <c r="M106" s="9"/>
+      <c r="N106" s="9"/>
+      <c r="O106" s="9"/>
+      <c r="P106" s="9"/>
+      <c r="Q106" s="9"/>
+      <c r="R106" s="9"/>
+      <c r="S106" s="9"/>
+      <c r="T106" s="9"/>
+      <c r="U106" s="9"/>
+      <c r="V106" s="9"/>
+      <c r="W106" s="9"/>
+      <c r="X106" s="9"/>
+      <c r="Y106" s="9"/>
+      <c r="Z106" s="9"/>
+      <c r="AA106" s="9"/>
+      <c r="AB106" s="9"/>
+      <c r="AC106" s="9"/>
+      <c r="AD106" s="9"/>
+      <c r="AE106" s="9"/>
+      <c r="AF106" s="9"/>
+      <c r="AG106" s="9"/>
+      <c r="AH106" s="9"/>
+    </row>
+    <row r="107" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A107" s="8">
+        <v>105</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G107" s="16">
+        <v>200</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J107" s="23"/>
+      <c r="K107" s="9"/>
+      <c r="L107" s="9"/>
+      <c r="M107" s="9"/>
+      <c r="N107" s="9"/>
+      <c r="O107" s="9"/>
+      <c r="P107" s="9"/>
+      <c r="Q107" s="9"/>
+      <c r="R107" s="9"/>
+      <c r="S107" s="9"/>
+      <c r="T107" s="9"/>
+      <c r="U107" s="9"/>
+      <c r="V107" s="9"/>
+      <c r="W107" s="9"/>
+      <c r="X107" s="9"/>
+      <c r="Y107" s="9"/>
+      <c r="Z107" s="9"/>
+      <c r="AA107" s="9"/>
+      <c r="AB107" s="9"/>
+      <c r="AC107" s="9"/>
+      <c r="AD107" s="9"/>
+      <c r="AE107" s="9"/>
+      <c r="AF107" s="9"/>
+      <c r="AG107" s="9"/>
+      <c r="AH107" s="9"/>
+    </row>
+    <row r="108" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A108" s="8">
+        <v>106</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E108" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F108" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I108" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J108" s="23"/>
+      <c r="K108" s="9"/>
+      <c r="L108" s="9"/>
+      <c r="M108" s="9"/>
+      <c r="N108" s="9"/>
+      <c r="O108" s="9"/>
+      <c r="P108" s="9"/>
+      <c r="Q108" s="9"/>
+      <c r="R108" s="9"/>
+      <c r="S108" s="9"/>
+      <c r="T108" s="9"/>
+      <c r="U108" s="9"/>
+      <c r="V108" s="9"/>
+      <c r="W108" s="9"/>
+      <c r="X108" s="9"/>
+      <c r="Y108" s="9"/>
+      <c r="Z108" s="9"/>
+      <c r="AA108" s="9"/>
+      <c r="AB108" s="9"/>
+      <c r="AC108" s="9"/>
+      <c r="AD108" s="9"/>
+      <c r="AE108" s="9"/>
+      <c r="AF108" s="9"/>
+      <c r="AG108" s="9"/>
+      <c r="AH108" s="9"/>
+    </row>
+    <row r="109" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A109" s="8">
+        <v>107</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E109" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J109" s="23"/>
+      <c r="K109" s="9"/>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9"/>
+      <c r="N109" s="9"/>
+      <c r="O109" s="9"/>
+      <c r="P109" s="9"/>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
+      <c r="V109" s="9"/>
+      <c r="W109" s="9"/>
+      <c r="X109" s="9"/>
+      <c r="Y109" s="9"/>
+      <c r="Z109" s="9"/>
+      <c r="AA109" s="9"/>
+      <c r="AB109" s="9"/>
+      <c r="AC109" s="9"/>
+      <c r="AD109" s="9"/>
+      <c r="AE109" s="9"/>
+      <c r="AF109" s="9"/>
+      <c r="AG109" s="9"/>
+      <c r="AH109" s="9"/>
+    </row>
+    <row r="110" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A110" s="8">
+        <v>108</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I110" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J110" s="23"/>
+      <c r="K110" s="9"/>
+      <c r="L110" s="9"/>
+      <c r="M110" s="9"/>
+      <c r="N110" s="9"/>
+      <c r="O110" s="9"/>
+      <c r="P110" s="9"/>
+      <c r="Q110" s="9"/>
+      <c r="R110" s="9"/>
+      <c r="S110" s="9"/>
+      <c r="T110" s="9"/>
+      <c r="U110" s="9"/>
+      <c r="V110" s="9"/>
+      <c r="W110" s="9"/>
+      <c r="X110" s="9"/>
+      <c r="Y110" s="9"/>
+      <c r="Z110" s="9"/>
+      <c r="AA110" s="9"/>
+      <c r="AB110" s="9"/>
+      <c r="AC110" s="9"/>
+      <c r="AD110" s="9"/>
+      <c r="AE110" s="9"/>
+      <c r="AF110" s="9"/>
+      <c r="AG110" s="9"/>
+      <c r="AH110" s="9"/>
+    </row>
+    <row r="111" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A111" s="8">
+        <v>109</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G111" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I111" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="J111" s="23"/>
+      <c r="K111" s="9"/>
+      <c r="L111" s="9"/>
+      <c r="M111" s="9"/>
+      <c r="N111" s="9"/>
+      <c r="O111" s="9"/>
+      <c r="P111" s="9"/>
+      <c r="Q111" s="9"/>
+      <c r="R111" s="9"/>
+      <c r="S111" s="9"/>
+      <c r="T111" s="9"/>
+      <c r="U111" s="9"/>
+      <c r="V111" s="9"/>
+      <c r="W111" s="9"/>
+      <c r="X111" s="9"/>
+      <c r="Y111" s="9"/>
+      <c r="Z111" s="9"/>
+      <c r="AA111" s="9"/>
+      <c r="AB111" s="9"/>
+      <c r="AC111" s="9"/>
+      <c r="AD111" s="9"/>
+      <c r="AE111" s="9"/>
+      <c r="AF111" s="9"/>
+      <c r="AG111" s="9"/>
+      <c r="AH111" s="9"/>
+    </row>
+    <row r="112" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A112" s="8">
+        <v>110</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G112" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="J112" s="23"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="9"/>
+      <c r="N112" s="9"/>
+      <c r="O112" s="9"/>
+      <c r="P112" s="9"/>
+      <c r="Q112" s="9"/>
+      <c r="R112" s="9"/>
+      <c r="S112" s="9"/>
+      <c r="T112" s="9"/>
+      <c r="U112" s="9"/>
+      <c r="V112" s="9"/>
+      <c r="W112" s="9"/>
+      <c r="X112" s="9"/>
+      <c r="Y112" s="9"/>
+      <c r="Z112" s="9"/>
+      <c r="AA112" s="9"/>
+      <c r="AB112" s="9"/>
+      <c r="AC112" s="9"/>
+      <c r="AD112" s="9"/>
+      <c r="AE112" s="9"/>
+      <c r="AF112" s="9"/>
+      <c r="AG112" s="9"/>
+      <c r="AH112" s="9"/>
+    </row>
+    <row r="113" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A113" s="8">
+        <v>111</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G113" s="17">
+        <v>400</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J113" s="23"/>
+      <c r="K113" s="9"/>
+      <c r="L113" s="9"/>
+      <c r="M113" s="9"/>
+      <c r="N113" s="9"/>
+      <c r="O113" s="9"/>
+      <c r="P113" s="9"/>
+      <c r="Q113" s="9"/>
+      <c r="R113" s="9"/>
+      <c r="S113" s="9"/>
+      <c r="T113" s="9"/>
+      <c r="U113" s="9"/>
+      <c r="V113" s="9"/>
+      <c r="W113" s="9"/>
+      <c r="X113" s="9"/>
+      <c r="Y113" s="9"/>
+      <c r="Z113" s="9"/>
+      <c r="AA113" s="9"/>
+      <c r="AB113" s="9"/>
+      <c r="AC113" s="9"/>
+      <c r="AD113" s="9"/>
+      <c r="AE113" s="9"/>
+      <c r="AF113" s="9"/>
+      <c r="AG113" s="9"/>
+      <c r="AH113" s="9"/>
+    </row>
+    <row r="114" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A114" s="8">
+        <v>112</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G114" s="2">
+        <v>550</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I114" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="J114" s="23"/>
+      <c r="K114" s="9"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="9"/>
+      <c r="N114" s="9"/>
+      <c r="O114" s="9"/>
+      <c r="P114" s="9"/>
+      <c r="Q114" s="9"/>
+      <c r="R114" s="9"/>
+      <c r="S114" s="9"/>
+      <c r="T114" s="9"/>
+      <c r="U114" s="9"/>
+      <c r="V114" s="9"/>
+      <c r="W114" s="9"/>
+      <c r="X114" s="9"/>
+      <c r="Y114" s="9"/>
+      <c r="Z114" s="9"/>
+      <c r="AA114" s="9"/>
+      <c r="AB114" s="9"/>
+      <c r="AC114" s="9"/>
+      <c r="AD114" s="9"/>
+      <c r="AE114" s="9"/>
+      <c r="AF114" s="9"/>
+      <c r="AG114" s="9"/>
+      <c r="AH114" s="9"/>
+    </row>
+    <row r="115" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A115" s="8">
+        <v>113</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G115" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I115" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J115" s="23"/>
+      <c r="K115" s="9"/>
+      <c r="L115" s="9"/>
+      <c r="M115" s="9"/>
+      <c r="N115" s="9"/>
+      <c r="O115" s="9"/>
+      <c r="P115" s="9"/>
+      <c r="Q115" s="9"/>
+      <c r="R115" s="9"/>
+      <c r="S115" s="9"/>
+      <c r="T115" s="9"/>
+      <c r="U115" s="9"/>
+      <c r="V115" s="9"/>
+      <c r="W115" s="9"/>
+      <c r="X115" s="9"/>
+      <c r="Y115" s="9"/>
+      <c r="Z115" s="9"/>
+      <c r="AA115" s="9"/>
+      <c r="AB115" s="9"/>
+      <c r="AC115" s="9"/>
+      <c r="AD115" s="9"/>
+      <c r="AE115" s="9"/>
+      <c r="AF115" s="9"/>
+      <c r="AG115" s="9"/>
+      <c r="AH115" s="9"/>
+    </row>
+    <row r="116" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A116" s="8">
+        <v>114</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G116" s="16">
+        <v>300</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I116" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="J116" s="23"/>
+      <c r="K116" s="9"/>
+      <c r="L116" s="9"/>
+      <c r="M116" s="9"/>
+      <c r="N116" s="9"/>
+      <c r="O116" s="9"/>
+      <c r="P116" s="9"/>
+      <c r="Q116" s="9"/>
+      <c r="R116" s="9"/>
+      <c r="S116" s="9"/>
+      <c r="T116" s="9"/>
+      <c r="U116" s="9"/>
+      <c r="V116" s="9"/>
+      <c r="W116" s="9"/>
+      <c r="X116" s="9"/>
+      <c r="Y116" s="9"/>
+      <c r="Z116" s="9"/>
+      <c r="AA116" s="9"/>
+      <c r="AB116" s="9"/>
+      <c r="AC116" s="9"/>
+      <c r="AD116" s="9"/>
+      <c r="AE116" s="9"/>
+      <c r="AF116" s="9"/>
+      <c r="AG116" s="9"/>
+      <c r="AH116" s="9"/>
+    </row>
+    <row r="117" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A117" s="8">
+        <v>115</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G117" s="16">
+        <v>350</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="J117" s="23"/>
+      <c r="K117" s="9"/>
+      <c r="L117" s="9"/>
+      <c r="M117" s="9"/>
+      <c r="N117" s="9"/>
+      <c r="O117" s="9"/>
+      <c r="P117" s="9"/>
+      <c r="Q117" s="9"/>
+      <c r="R117" s="9"/>
+      <c r="S117" s="9"/>
+      <c r="T117" s="9"/>
+      <c r="U117" s="9"/>
+      <c r="V117" s="9"/>
+      <c r="W117" s="9"/>
+      <c r="X117" s="9"/>
+      <c r="Y117" s="9"/>
+      <c r="Z117" s="9"/>
+      <c r="AA117" s="9"/>
+      <c r="AB117" s="9"/>
+      <c r="AC117" s="9"/>
+      <c r="AD117" s="9"/>
+      <c r="AE117" s="9"/>
+      <c r="AF117" s="9"/>
+      <c r="AG117" s="9"/>
+      <c r="AH117" s="9"/>
+    </row>
+    <row r="118" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A118" s="8">
+        <v>116</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E118" s="3">
+        <v>500</v>
+      </c>
+      <c r="F118" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J118" s="23"/>
+      <c r="K118" s="9"/>
+      <c r="L118" s="9"/>
+      <c r="M118" s="9"/>
+      <c r="N118" s="9"/>
+      <c r="O118" s="9"/>
+      <c r="P118" s="9"/>
+      <c r="Q118" s="9"/>
+      <c r="R118" s="9"/>
+      <c r="S118" s="9"/>
+      <c r="T118" s="9"/>
+      <c r="U118" s="9"/>
+      <c r="V118" s="9"/>
+      <c r="W118" s="9"/>
+      <c r="X118" s="9"/>
+      <c r="Y118" s="9"/>
+      <c r="Z118" s="9"/>
+      <c r="AA118" s="9"/>
+      <c r="AB118" s="9"/>
+      <c r="AC118" s="9"/>
+      <c r="AD118" s="9"/>
+      <c r="AE118" s="9"/>
+      <c r="AF118" s="9"/>
+      <c r="AG118" s="9"/>
+      <c r="AH118" s="9"/>
+    </row>
+    <row r="119" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A119" s="8">
+        <v>117</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I119" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="J119" s="23"/>
+      <c r="K119" s="9"/>
+      <c r="L119" s="9"/>
+      <c r="M119" s="9"/>
+      <c r="N119" s="9"/>
+      <c r="O119" s="9"/>
+      <c r="P119" s="9"/>
+      <c r="Q119" s="9"/>
+      <c r="R119" s="9"/>
+      <c r="S119" s="9"/>
+      <c r="T119" s="9"/>
+      <c r="U119" s="9"/>
+      <c r="V119" s="9"/>
+      <c r="W119" s="9"/>
+      <c r="X119" s="9"/>
+      <c r="Y119" s="9"/>
+      <c r="Z119" s="9"/>
+      <c r="AA119" s="9"/>
+      <c r="AB119" s="9"/>
+      <c r="AC119" s="9"/>
+      <c r="AD119" s="9"/>
+      <c r="AE119" s="9"/>
+      <c r="AF119" s="9"/>
+      <c r="AG119" s="9"/>
+      <c r="AH119" s="9"/>
+    </row>
+    <row r="120" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A120" s="8">
+        <v>118</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G120" s="2">
+        <v>200</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J120" s="23"/>
+      <c r="K120" s="9"/>
+      <c r="L120" s="9"/>
+      <c r="M120" s="9"/>
+      <c r="N120" s="9"/>
+      <c r="O120" s="9"/>
+      <c r="P120" s="9"/>
+      <c r="Q120" s="9"/>
+      <c r="R120" s="9"/>
+      <c r="S120" s="9"/>
+      <c r="T120" s="9"/>
+      <c r="U120" s="9"/>
+      <c r="V120" s="9"/>
+      <c r="W120" s="9"/>
+      <c r="X120" s="9"/>
+      <c r="Y120" s="9"/>
+      <c r="Z120" s="9"/>
+      <c r="AA120" s="9"/>
+      <c r="AB120" s="9"/>
+      <c r="AC120" s="9"/>
+      <c r="AD120" s="9"/>
+      <c r="AE120" s="9"/>
+      <c r="AF120" s="9"/>
+      <c r="AG120" s="9"/>
+      <c r="AH120" s="9"/>
+    </row>
+    <row r="121" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A121" s="8">
+        <v>119</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G121" s="16">
+        <v>220</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J121" s="23"/>
+      <c r="K121" s="9"/>
+      <c r="L121" s="9"/>
+      <c r="M121" s="9"/>
+      <c r="N121" s="9"/>
+      <c r="O121" s="9"/>
+      <c r="P121" s="9"/>
+      <c r="Q121" s="9"/>
+      <c r="R121" s="9"/>
+      <c r="S121" s="9"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
+      <c r="V121" s="9"/>
+      <c r="W121" s="9"/>
+      <c r="X121" s="9"/>
+      <c r="Y121" s="9"/>
+      <c r="Z121" s="9"/>
+      <c r="AA121" s="9"/>
+      <c r="AB121" s="9"/>
+      <c r="AC121" s="9"/>
+      <c r="AD121" s="9"/>
+      <c r="AE121" s="9"/>
+      <c r="AF121" s="9"/>
+      <c r="AG121" s="9"/>
+      <c r="AH121" s="9"/>
+    </row>
+    <row r="122" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A122" s="8">
+        <v>120</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G122" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J122" s="23"/>
+      <c r="K122" s="9"/>
+      <c r="L122" s="9"/>
+      <c r="M122" s="9"/>
+      <c r="N122" s="9"/>
+      <c r="O122" s="9"/>
+      <c r="P122" s="9"/>
+      <c r="Q122" s="9"/>
+      <c r="R122" s="9"/>
+      <c r="S122" s="9"/>
+      <c r="T122" s="9"/>
+      <c r="U122" s="9"/>
+      <c r="V122" s="9"/>
+      <c r="W122" s="9"/>
+      <c r="X122" s="9"/>
+      <c r="Y122" s="9"/>
+      <c r="Z122" s="9"/>
+      <c r="AA122" s="9"/>
+      <c r="AB122" s="9"/>
+      <c r="AC122" s="9"/>
+      <c r="AD122" s="9"/>
+      <c r="AE122" s="9"/>
+      <c r="AF122" s="9"/>
+      <c r="AG122" s="9"/>
+      <c r="AH122" s="9"/>
+    </row>
+    <row r="123" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A123" s="8">
+        <v>121</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I123" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="J123" s="23"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
+      <c r="M123" s="9"/>
+      <c r="N123" s="9"/>
+      <c r="O123" s="9"/>
+      <c r="P123" s="9"/>
+      <c r="Q123" s="9"/>
+      <c r="R123" s="9"/>
+      <c r="S123" s="9"/>
+      <c r="T123" s="9"/>
+      <c r="U123" s="9"/>
+      <c r="V123" s="9"/>
+      <c r="W123" s="9"/>
+      <c r="X123" s="9"/>
+      <c r="Y123" s="9"/>
+      <c r="Z123" s="9"/>
+      <c r="AA123" s="9"/>
+      <c r="AB123" s="9"/>
+      <c r="AC123" s="9"/>
+      <c r="AD123" s="9"/>
+      <c r="AE123" s="9"/>
+      <c r="AF123" s="9"/>
+      <c r="AG123" s="9"/>
+      <c r="AH123" s="9"/>
+    </row>
+    <row r="124" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A124" s="8">
+        <v>122</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G124" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J124" s="23"/>
+      <c r="K124" s="9"/>
+      <c r="L124" s="9"/>
+      <c r="M124" s="9"/>
+      <c r="N124" s="9"/>
+      <c r="O124" s="9"/>
+      <c r="P124" s="9"/>
+      <c r="Q124" s="9"/>
+      <c r="R124" s="9"/>
+      <c r="S124" s="9"/>
+      <c r="T124" s="9"/>
+      <c r="U124" s="9"/>
+      <c r="V124" s="9"/>
+      <c r="W124" s="9"/>
+      <c r="X124" s="9"/>
+      <c r="Y124" s="9"/>
+      <c r="Z124" s="9"/>
+      <c r="AA124" s="9"/>
+      <c r="AB124" s="9"/>
+      <c r="AC124" s="9"/>
+      <c r="AD124" s="9"/>
+      <c r="AE124" s="9"/>
+      <c r="AF124" s="9"/>
+      <c r="AG124" s="9"/>
+      <c r="AH124" s="9"/>
+    </row>
+    <row r="125" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A125" s="8">
+        <v>123</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F125" s="24">
+        <v>2199</v>
+      </c>
+      <c r="G125" s="3">
+        <v>200</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I125" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="J125" s="23"/>
+      <c r="K125" s="9"/>
+      <c r="L125" s="9"/>
+      <c r="M125" s="9"/>
+      <c r="N125" s="9"/>
+      <c r="O125" s="9"/>
+      <c r="P125" s="9"/>
+      <c r="Q125" s="9"/>
+      <c r="R125" s="9"/>
+      <c r="S125" s="9"/>
+      <c r="T125" s="9"/>
+      <c r="U125" s="9"/>
+      <c r="V125" s="9"/>
+      <c r="W125" s="9"/>
+      <c r="X125" s="9"/>
+      <c r="Y125" s="9"/>
+      <c r="Z125" s="9"/>
+      <c r="AA125" s="9"/>
+      <c r="AB125" s="9"/>
+      <c r="AC125" s="9"/>
+      <c r="AD125" s="9"/>
+      <c r="AE125" s="9"/>
+      <c r="AF125" s="9"/>
+      <c r="AG125" s="9"/>
+      <c r="AH125" s="9"/>
+    </row>
+    <row r="126" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A126" s="8">
+        <v>124</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="J126" s="23"/>
+      <c r="K126" s="9"/>
+      <c r="L126" s="9"/>
+      <c r="M126" s="9"/>
+      <c r="N126" s="9"/>
+      <c r="O126" s="9"/>
+      <c r="P126" s="9"/>
+      <c r="Q126" s="9"/>
+      <c r="R126" s="9"/>
+      <c r="S126" s="9"/>
+      <c r="T126" s="9"/>
+      <c r="U126" s="9"/>
+      <c r="V126" s="9"/>
+      <c r="W126" s="9"/>
+      <c r="X126" s="9"/>
+      <c r="Y126" s="9"/>
+      <c r="Z126" s="9"/>
+      <c r="AA126" s="9"/>
+      <c r="AB126" s="9"/>
+      <c r="AC126" s="9"/>
+      <c r="AD126" s="9"/>
+      <c r="AE126" s="9"/>
+      <c r="AF126" s="9"/>
+      <c r="AG126" s="9"/>
+      <c r="AH126" s="9"/>
+    </row>
+    <row r="127" spans="1:34" ht="219" thickBot="1">
+      <c r="A127" s="8">
+        <v>125</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J127" s="23"/>
+      <c r="K127" s="9"/>
+      <c r="L127" s="9"/>
+      <c r="M127" s="9"/>
+      <c r="N127" s="9"/>
+      <c r="O127" s="9"/>
+      <c r="P127" s="9"/>
+      <c r="Q127" s="9"/>
+      <c r="R127" s="9"/>
+      <c r="S127" s="9"/>
+      <c r="T127" s="9"/>
+      <c r="U127" s="9"/>
+      <c r="V127" s="9"/>
+      <c r="W127" s="9"/>
+      <c r="X127" s="9"/>
+      <c r="Y127" s="9"/>
+      <c r="Z127" s="9"/>
+      <c r="AA127" s="9"/>
+      <c r="AB127" s="9"/>
+      <c r="AC127" s="9"/>
+      <c r="AD127" s="9"/>
+      <c r="AE127" s="9"/>
+      <c r="AF127" s="9"/>
+      <c r="AG127" s="9"/>
+      <c r="AH127" s="9"/>
+    </row>
+    <row r="128" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A128" s="8">
+        <v>126</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J128" s="23"/>
+      <c r="K128" s="9"/>
+      <c r="L128" s="9"/>
+      <c r="M128" s="9"/>
+      <c r="N128" s="9"/>
+      <c r="O128" s="9"/>
+      <c r="P128" s="9"/>
+      <c r="Q128" s="9"/>
+      <c r="R128" s="9"/>
+      <c r="S128" s="9"/>
+      <c r="T128" s="9"/>
+      <c r="U128" s="9"/>
+      <c r="V128" s="9"/>
+      <c r="W128" s="9"/>
+      <c r="X128" s="9"/>
+      <c r="Y128" s="9"/>
+      <c r="Z128" s="9"/>
+      <c r="AA128" s="9"/>
+      <c r="AB128" s="9"/>
+      <c r="AC128" s="9"/>
+      <c r="AD128" s="9"/>
+      <c r="AE128" s="9"/>
+      <c r="AF128" s="9"/>
+      <c r="AG128" s="9"/>
+      <c r="AH128" s="9"/>
+    </row>
+    <row r="129" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A129" s="8">
+        <v>127</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I129" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J129" s="23"/>
+      <c r="K129" s="9"/>
+      <c r="L129" s="9"/>
+      <c r="M129" s="9"/>
+      <c r="N129" s="9"/>
+      <c r="O129" s="9"/>
+      <c r="P129" s="9"/>
+      <c r="Q129" s="9"/>
+      <c r="R129" s="9"/>
+      <c r="S129" s="9"/>
+      <c r="T129" s="9"/>
+      <c r="U129" s="9"/>
+      <c r="V129" s="9"/>
+      <c r="W129" s="9"/>
+      <c r="X129" s="9"/>
+      <c r="Y129" s="9"/>
+      <c r="Z129" s="9"/>
+      <c r="AA129" s="9"/>
+      <c r="AB129" s="9"/>
+      <c r="AC129" s="9"/>
+      <c r="AD129" s="9"/>
+      <c r="AE129" s="9"/>
+      <c r="AF129" s="9"/>
+      <c r="AG129" s="9"/>
+      <c r="AH129" s="9"/>
+    </row>
+    <row r="130" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A130" s="8">
+        <v>128</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I130" s="25"/>
+      <c r="J130" s="23"/>
+      <c r="K130" s="9"/>
+      <c r="L130" s="9"/>
+      <c r="M130" s="9"/>
+      <c r="N130" s="9"/>
+      <c r="O130" s="9"/>
+      <c r="P130" s="9"/>
+      <c r="Q130" s="9"/>
+      <c r="R130" s="9"/>
+      <c r="S130" s="9"/>
+      <c r="T130" s="9"/>
+      <c r="U130" s="9"/>
+      <c r="V130" s="9"/>
+      <c r="W130" s="9"/>
+      <c r="X130" s="9"/>
+      <c r="Y130" s="9"/>
+      <c r="Z130" s="9"/>
+      <c r="AA130" s="9"/>
+      <c r="AB130" s="9"/>
+      <c r="AC130" s="9"/>
+      <c r="AD130" s="9"/>
+      <c r="AE130" s="9"/>
+      <c r="AF130" s="9"/>
+      <c r="AG130" s="9"/>
+      <c r="AH130" s="9"/>
+    </row>
+    <row r="131" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A131" s="8">
+        <v>129</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I131" s="25"/>
+      <c r="J131" s="23"/>
+      <c r="K131" s="9"/>
+      <c r="L131" s="9"/>
+      <c r="M131" s="9"/>
+      <c r="N131" s="9"/>
+      <c r="O131" s="9"/>
+      <c r="P131" s="9"/>
+      <c r="Q131" s="9"/>
+      <c r="R131" s="9"/>
+      <c r="S131" s="9"/>
+      <c r="T131" s="9"/>
+      <c r="U131" s="9"/>
+      <c r="V131" s="9"/>
+      <c r="W131" s="9"/>
+      <c r="X131" s="9"/>
+      <c r="Y131" s="9"/>
+      <c r="Z131" s="9"/>
+      <c r="AA131" s="9"/>
+      <c r="AB131" s="9"/>
+      <c r="AC131" s="9"/>
+      <c r="AD131" s="9"/>
+      <c r="AE131" s="9"/>
+      <c r="AF131" s="9"/>
+      <c r="AG131" s="9"/>
+      <c r="AH131" s="9"/>
+    </row>
+    <row r="132" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A132" s="8">
+        <v>130</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I132" s="25"/>
+      <c r="J132" s="23"/>
+      <c r="K132" s="9"/>
+      <c r="L132" s="9"/>
+      <c r="M132" s="9"/>
+      <c r="N132" s="9"/>
+      <c r="O132" s="9"/>
+      <c r="P132" s="9"/>
+      <c r="Q132" s="9"/>
+      <c r="R132" s="9"/>
+      <c r="S132" s="9"/>
+      <c r="T132" s="9"/>
+      <c r="U132" s="9"/>
+      <c r="V132" s="9"/>
+      <c r="W132" s="9"/>
+      <c r="X132" s="9"/>
+      <c r="Y132" s="9"/>
+      <c r="Z132" s="9"/>
+      <c r="AA132" s="9"/>
+      <c r="AB132" s="9"/>
+      <c r="AC132" s="9"/>
+      <c r="AD132" s="9"/>
+      <c r="AE132" s="9"/>
+      <c r="AF132" s="9"/>
+      <c r="AG132" s="9"/>
+      <c r="AH132" s="9"/>
+    </row>
+    <row r="133" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A133" s="8">
+        <v>131</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I133" s="25"/>
+      <c r="J133" s="23"/>
+      <c r="K133" s="9"/>
+      <c r="L133" s="9"/>
+      <c r="M133" s="9"/>
+      <c r="N133" s="9"/>
+      <c r="O133" s="9"/>
+      <c r="P133" s="9"/>
+      <c r="Q133" s="9"/>
+      <c r="R133" s="9"/>
+      <c r="S133" s="9"/>
+      <c r="T133" s="9"/>
+      <c r="U133" s="9"/>
+      <c r="V133" s="9"/>
+      <c r="W133" s="9"/>
+      <c r="X133" s="9"/>
+      <c r="Y133" s="9"/>
+      <c r="Z133" s="9"/>
+      <c r="AA133" s="9"/>
+      <c r="AB133" s="9"/>
+      <c r="AC133" s="9"/>
+      <c r="AD133" s="9"/>
+      <c r="AE133" s="9"/>
+      <c r="AF133" s="9"/>
+      <c r="AG133" s="9"/>
+      <c r="AH133" s="9"/>
+    </row>
+    <row r="134" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A134" s="8">
+        <v>132</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I134" s="25"/>
+      <c r="J134" s="23"/>
+      <c r="K134" s="9"/>
+      <c r="L134" s="9"/>
+      <c r="M134" s="9"/>
+      <c r="N134" s="9"/>
+      <c r="O134" s="9"/>
+      <c r="P134" s="9"/>
+      <c r="Q134" s="9"/>
+      <c r="R134" s="9"/>
+      <c r="S134" s="9"/>
+      <c r="T134" s="9"/>
+      <c r="U134" s="9"/>
+      <c r="V134" s="9"/>
+      <c r="W134" s="9"/>
+      <c r="X134" s="9"/>
+      <c r="Y134" s="9"/>
+      <c r="Z134" s="9"/>
+      <c r="AA134" s="9"/>
+      <c r="AB134" s="9"/>
+      <c r="AC134" s="9"/>
+      <c r="AD134" s="9"/>
+      <c r="AE134" s="9"/>
+      <c r="AF134" s="9"/>
+      <c r="AG134" s="9"/>
+      <c r="AH134" s="9"/>
+    </row>
+    <row r="135" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A135" s="8">
+        <v>133</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I135" s="25"/>
+      <c r="J135" s="23"/>
+      <c r="K135" s="9"/>
+      <c r="L135" s="9"/>
+      <c r="M135" s="9"/>
+      <c r="N135" s="9"/>
+      <c r="O135" s="9"/>
+      <c r="P135" s="9"/>
+      <c r="Q135" s="9"/>
+      <c r="R135" s="9"/>
+      <c r="S135" s="9"/>
+      <c r="T135" s="9"/>
+      <c r="U135" s="9"/>
+      <c r="V135" s="9"/>
+      <c r="W135" s="9"/>
+      <c r="X135" s="9"/>
+      <c r="Y135" s="9"/>
+      <c r="Z135" s="9"/>
+      <c r="AA135" s="9"/>
+      <c r="AB135" s="9"/>
+      <c r="AC135" s="9"/>
+      <c r="AD135" s="9"/>
+      <c r="AE135" s="9"/>
+      <c r="AF135" s="9"/>
+      <c r="AG135" s="9"/>
+      <c r="AH135" s="9"/>
+    </row>
+    <row r="136" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A136" s="8">
+        <v>134</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I136" s="25"/>
+      <c r="J136" s="23"/>
+      <c r="K136" s="9"/>
+      <c r="L136" s="9"/>
+      <c r="M136" s="9"/>
+      <c r="N136" s="9"/>
+      <c r="O136" s="9"/>
+      <c r="P136" s="9"/>
+      <c r="Q136" s="9"/>
+      <c r="R136" s="9"/>
+      <c r="S136" s="9"/>
+      <c r="T136" s="9"/>
+      <c r="U136" s="9"/>
+      <c r="V136" s="9"/>
+      <c r="W136" s="9"/>
+      <c r="X136" s="9"/>
+      <c r="Y136" s="9"/>
+      <c r="Z136" s="9"/>
+      <c r="AA136" s="9"/>
+      <c r="AB136" s="9"/>
+      <c r="AC136" s="9"/>
+      <c r="AD136" s="9"/>
+      <c r="AE136" s="9"/>
+      <c r="AF136" s="9"/>
+      <c r="AG136" s="9"/>
+      <c r="AH136" s="9"/>
+    </row>
+    <row r="137" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A137" s="8">
+        <v>135</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I137" s="25"/>
+      <c r="J137" s="23"/>
+      <c r="K137" s="9"/>
+      <c r="L137" s="9"/>
+      <c r="M137" s="9"/>
+      <c r="N137" s="9"/>
+      <c r="O137" s="9"/>
+      <c r="P137" s="9"/>
+      <c r="Q137" s="9"/>
+      <c r="R137" s="9"/>
+      <c r="S137" s="9"/>
+      <c r="T137" s="9"/>
+      <c r="U137" s="9"/>
+      <c r="V137" s="9"/>
+      <c r="W137" s="9"/>
+      <c r="X137" s="9"/>
+      <c r="Y137" s="9"/>
+      <c r="Z137" s="9"/>
+      <c r="AA137" s="9"/>
+      <c r="AB137" s="9"/>
+      <c r="AC137" s="9"/>
+      <c r="AD137" s="9"/>
+      <c r="AE137" s="9"/>
+      <c r="AF137" s="9"/>
+      <c r="AG137" s="9"/>
+      <c r="AH137" s="9"/>
+    </row>
+    <row r="138" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A138" s="8">
+        <v>136</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I138" s="25"/>
+      <c r="J138" s="23"/>
+      <c r="K138" s="9"/>
+      <c r="L138" s="9"/>
+      <c r="M138" s="9"/>
+      <c r="N138" s="9"/>
+      <c r="O138" s="9"/>
+      <c r="P138" s="9"/>
+      <c r="Q138" s="9"/>
+      <c r="R138" s="9"/>
+      <c r="S138" s="9"/>
+      <c r="T138" s="9"/>
+      <c r="U138" s="9"/>
+      <c r="V138" s="9"/>
+      <c r="W138" s="9"/>
+      <c r="X138" s="9"/>
+      <c r="Y138" s="9"/>
+      <c r="Z138" s="9"/>
+      <c r="AA138" s="9"/>
+      <c r="AB138" s="9"/>
+      <c r="AC138" s="9"/>
+      <c r="AD138" s="9"/>
+      <c r="AE138" s="9"/>
+      <c r="AF138" s="9"/>
+      <c r="AG138" s="9"/>
+      <c r="AH138" s="9"/>
+    </row>
+    <row r="139" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A139" s="8">
+        <v>137</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I139" s="25"/>
+      <c r="J139" s="23"/>
+      <c r="K139" s="9"/>
+      <c r="L139" s="9"/>
+      <c r="M139" s="9"/>
+      <c r="N139" s="9"/>
+      <c r="O139" s="9"/>
+      <c r="P139" s="9"/>
+      <c r="Q139" s="9"/>
+      <c r="R139" s="9"/>
+      <c r="S139" s="9"/>
+      <c r="T139" s="9"/>
+      <c r="U139" s="9"/>
+      <c r="V139" s="9"/>
+      <c r="W139" s="9"/>
+      <c r="X139" s="9"/>
+      <c r="Y139" s="9"/>
+      <c r="Z139" s="9"/>
+      <c r="AA139" s="9"/>
+      <c r="AB139" s="9"/>
+      <c r="AC139" s="9"/>
+      <c r="AD139" s="9"/>
+      <c r="AE139" s="9"/>
+      <c r="AF139" s="9"/>
+      <c r="AG139" s="9"/>
+      <c r="AH139" s="9"/>
+    </row>
+    <row r="140" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A140" s="8">
+        <v>138</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I140" s="25"/>
+      <c r="J140" s="23"/>
+      <c r="K140" s="9"/>
+      <c r="L140" s="9"/>
+      <c r="M140" s="9"/>
+      <c r="N140" s="9"/>
+      <c r="O140" s="9"/>
+      <c r="P140" s="9"/>
+      <c r="Q140" s="9"/>
+      <c r="R140" s="9"/>
+      <c r="S140" s="9"/>
+      <c r="T140" s="9"/>
+      <c r="U140" s="9"/>
+      <c r="V140" s="9"/>
+      <c r="W140" s="9"/>
+      <c r="X140" s="9"/>
+      <c r="Y140" s="9"/>
+      <c r="Z140" s="9"/>
+      <c r="AA140" s="9"/>
+      <c r="AB140" s="9"/>
+      <c r="AC140" s="9"/>
+      <c r="AD140" s="9"/>
+      <c r="AE140" s="9"/>
+      <c r="AF140" s="9"/>
+      <c r="AG140" s="9"/>
+      <c r="AH140" s="9"/>
+    </row>
+    <row r="141" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A141" s="8">
+        <v>139</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I141" s="25"/>
+      <c r="J141" s="23"/>
+      <c r="K141" s="9"/>
+      <c r="L141" s="9"/>
+      <c r="M141" s="9"/>
+      <c r="N141" s="9"/>
+      <c r="O141" s="9"/>
+      <c r="P141" s="9"/>
+      <c r="Q141" s="9"/>
+      <c r="R141" s="9"/>
+      <c r="S141" s="9"/>
+      <c r="T141" s="9"/>
+      <c r="U141" s="9"/>
+      <c r="V141" s="9"/>
+      <c r="W141" s="9"/>
+      <c r="X141" s="9"/>
+      <c r="Y141" s="9"/>
+      <c r="Z141" s="9"/>
+      <c r="AA141" s="9"/>
+      <c r="AB141" s="9"/>
+      <c r="AC141" s="9"/>
+      <c r="AD141" s="9"/>
+      <c r="AE141" s="9"/>
+      <c r="AF141" s="9"/>
+      <c r="AG141" s="9"/>
+      <c r="AH141" s="9"/>
+    </row>
+    <row r="142" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A142" s="8">
+        <v>140</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I142" s="25"/>
+      <c r="J142" s="23"/>
+      <c r="K142" s="9"/>
+      <c r="L142" s="9"/>
+      <c r="M142" s="9"/>
+      <c r="N142" s="9"/>
+      <c r="O142" s="9"/>
+      <c r="P142" s="9"/>
+      <c r="Q142" s="9"/>
+      <c r="R142" s="9"/>
+      <c r="S142" s="9"/>
+      <c r="T142" s="9"/>
+      <c r="U142" s="9"/>
+      <c r="V142" s="9"/>
+      <c r="W142" s="9"/>
+      <c r="X142" s="9"/>
+      <c r="Y142" s="9"/>
+      <c r="Z142" s="9"/>
+      <c r="AA142" s="9"/>
+      <c r="AB142" s="9"/>
+      <c r="AC142" s="9"/>
+      <c r="AD142" s="9"/>
+      <c r="AE142" s="9"/>
+      <c r="AF142" s="9"/>
+      <c r="AG142" s="9"/>
+      <c r="AH142" s="9"/>
+    </row>
+    <row r="143" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A143" s="8">
+        <v>141</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I143" s="25"/>
+      <c r="J143" s="23"/>
+      <c r="K143" s="9"/>
+      <c r="L143" s="9"/>
+      <c r="M143" s="9"/>
+      <c r="N143" s="9"/>
+      <c r="O143" s="9"/>
+      <c r="P143" s="9"/>
+      <c r="Q143" s="9"/>
+      <c r="R143" s="9"/>
+      <c r="S143" s="9"/>
+      <c r="T143" s="9"/>
+      <c r="U143" s="9"/>
+      <c r="V143" s="9"/>
+      <c r="W143" s="9"/>
+      <c r="X143" s="9"/>
+      <c r="Y143" s="9"/>
+      <c r="Z143" s="9"/>
+      <c r="AA143" s="9"/>
+      <c r="AB143" s="9"/>
+      <c r="AC143" s="9"/>
+      <c r="AD143" s="9"/>
+      <c r="AE143" s="9"/>
+      <c r="AF143" s="9"/>
+      <c r="AG143" s="9"/>
+      <c r="AH143" s="9"/>
+    </row>
+    <row r="144" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A144" s="8">
+        <v>142</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I144" s="25"/>
+      <c r="J144" s="23"/>
+      <c r="K144" s="9"/>
+      <c r="L144" s="9"/>
+      <c r="M144" s="9"/>
+      <c r="N144" s="9"/>
+      <c r="O144" s="9"/>
+      <c r="P144" s="9"/>
+      <c r="Q144" s="9"/>
+      <c r="R144" s="9"/>
+      <c r="S144" s="9"/>
+      <c r="T144" s="9"/>
+      <c r="U144" s="9"/>
+      <c r="V144" s="9"/>
+      <c r="W144" s="9"/>
+      <c r="X144" s="9"/>
+      <c r="Y144" s="9"/>
+      <c r="Z144" s="9"/>
+      <c r="AA144" s="9"/>
+      <c r="AB144" s="9"/>
+      <c r="AC144" s="9"/>
+      <c r="AD144" s="9"/>
+      <c r="AE144" s="9"/>
+      <c r="AF144" s="9"/>
+      <c r="AG144" s="9"/>
+      <c r="AH144" s="9"/>
+    </row>
+    <row r="145" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A145" s="8">
+        <v>143</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I145" s="25"/>
+      <c r="J145" s="23"/>
+      <c r="K145" s="9"/>
+      <c r="L145" s="9"/>
+      <c r="M145" s="9"/>
+      <c r="N145" s="9"/>
+      <c r="O145" s="9"/>
+      <c r="P145" s="9"/>
+      <c r="Q145" s="9"/>
+      <c r="R145" s="9"/>
+      <c r="S145" s="9"/>
+      <c r="T145" s="9"/>
+      <c r="U145" s="9"/>
+      <c r="V145" s="9"/>
+      <c r="W145" s="9"/>
+      <c r="X145" s="9"/>
+      <c r="Y145" s="9"/>
+      <c r="Z145" s="9"/>
+      <c r="AA145" s="9"/>
+      <c r="AB145" s="9"/>
+      <c r="AC145" s="9"/>
+      <c r="AD145" s="9"/>
+      <c r="AE145" s="9"/>
+      <c r="AF145" s="9"/>
+      <c r="AG145" s="9"/>
+      <c r="AH145" s="9"/>
+    </row>
+    <row r="146" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A146" s="8">
+        <v>144</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I146" s="25"/>
+      <c r="J146" s="23"/>
+      <c r="K146" s="9"/>
+      <c r="L146" s="9"/>
+      <c r="M146" s="9"/>
+      <c r="N146" s="9"/>
+      <c r="O146" s="9"/>
+      <c r="P146" s="9"/>
+      <c r="Q146" s="9"/>
+      <c r="R146" s="9"/>
+      <c r="S146" s="9"/>
+      <c r="T146" s="9"/>
+      <c r="U146" s="9"/>
+      <c r="V146" s="9"/>
+      <c r="W146" s="9"/>
+      <c r="X146" s="9"/>
+      <c r="Y146" s="9"/>
+      <c r="Z146" s="9"/>
+      <c r="AA146" s="9"/>
+      <c r="AB146" s="9"/>
+      <c r="AC146" s="9"/>
+      <c r="AD146" s="9"/>
+      <c r="AE146" s="9"/>
+      <c r="AF146" s="9"/>
+      <c r="AG146" s="9"/>
+      <c r="AH146" s="9"/>
+    </row>
+    <row r="147" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A147" s="8">
+        <v>145</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I147" s="25"/>
+      <c r="J147" s="23"/>
+      <c r="K147" s="9"/>
+      <c r="L147" s="9"/>
+      <c r="M147" s="9"/>
+      <c r="N147" s="9"/>
+      <c r="O147" s="9"/>
+      <c r="P147" s="9"/>
+      <c r="Q147" s="9"/>
+      <c r="R147" s="9"/>
+      <c r="S147" s="9"/>
+      <c r="T147" s="9"/>
+      <c r="U147" s="9"/>
+      <c r="V147" s="9"/>
+      <c r="W147" s="9"/>
+      <c r="X147" s="9"/>
+      <c r="Y147" s="9"/>
+      <c r="Z147" s="9"/>
+      <c r="AA147" s="9"/>
+      <c r="AB147" s="9"/>
+      <c r="AC147" s="9"/>
+      <c r="AD147" s="9"/>
+      <c r="AE147" s="9"/>
+      <c r="AF147" s="9"/>
+      <c r="AG147" s="9"/>
+      <c r="AH147" s="9"/>
+    </row>
+    <row r="148" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A148" s="8">
+        <v>146</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I148" s="25"/>
+      <c r="J148" s="23"/>
+      <c r="K148" s="9"/>
+      <c r="L148" s="9"/>
+      <c r="M148" s="9"/>
+      <c r="N148" s="9"/>
+      <c r="O148" s="9"/>
+      <c r="P148" s="9"/>
+      <c r="Q148" s="9"/>
+      <c r="R148" s="9"/>
+      <c r="S148" s="9"/>
+      <c r="T148" s="9"/>
+      <c r="U148" s="9"/>
+      <c r="V148" s="9"/>
+      <c r="W148" s="9"/>
+      <c r="X148" s="9"/>
+      <c r="Y148" s="9"/>
+      <c r="Z148" s="9"/>
+      <c r="AA148" s="9"/>
+      <c r="AB148" s="9"/>
+      <c r="AC148" s="9"/>
+      <c r="AD148" s="9"/>
+      <c r="AE148" s="9"/>
+      <c r="AF148" s="9"/>
+      <c r="AG148" s="9"/>
+      <c r="AH148" s="9"/>
+    </row>
+    <row r="149" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A149" s="8">
+        <v>147</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I149" s="25"/>
+      <c r="J149" s="23"/>
+      <c r="K149" s="9"/>
+      <c r="L149" s="9"/>
+      <c r="M149" s="9"/>
+      <c r="N149" s="9"/>
+      <c r="O149" s="9"/>
+      <c r="P149" s="9"/>
+      <c r="Q149" s="9"/>
+      <c r="R149" s="9"/>
+      <c r="S149" s="9"/>
+      <c r="T149" s="9"/>
+      <c r="U149" s="9"/>
+      <c r="V149" s="9"/>
+      <c r="W149" s="9"/>
+      <c r="X149" s="9"/>
+      <c r="Y149" s="9"/>
+      <c r="Z149" s="9"/>
+      <c r="AA149" s="9"/>
+      <c r="AB149" s="9"/>
+      <c r="AC149" s="9"/>
+      <c r="AD149" s="9"/>
+      <c r="AE149" s="9"/>
+      <c r="AF149" s="9"/>
+      <c r="AG149" s="9"/>
+      <c r="AH149" s="9"/>
+    </row>
+    <row r="150" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A150" s="8">
+        <v>148</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I150" s="25"/>
+      <c r="J150" s="23"/>
+      <c r="K150" s="9"/>
+      <c r="L150" s="9"/>
+      <c r="M150" s="9"/>
+      <c r="N150" s="9"/>
+      <c r="O150" s="9"/>
+      <c r="P150" s="9"/>
+      <c r="Q150" s="9"/>
+      <c r="R150" s="9"/>
+      <c r="S150" s="9"/>
+      <c r="T150" s="9"/>
+      <c r="U150" s="9"/>
+      <c r="V150" s="9"/>
+      <c r="W150" s="9"/>
+      <c r="X150" s="9"/>
+      <c r="Y150" s="9"/>
+      <c r="Z150" s="9"/>
+      <c r="AA150" s="9"/>
+      <c r="AB150" s="9"/>
+      <c r="AC150" s="9"/>
+      <c r="AD150" s="9"/>
+      <c r="AE150" s="9"/>
+      <c r="AF150" s="9"/>
+      <c r="AG150" s="9"/>
+      <c r="AH150" s="9"/>
+    </row>
+    <row r="151" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A151" s="8">
+        <v>149</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I151" s="25"/>
+      <c r="J151" s="23"/>
+      <c r="K151" s="9"/>
+      <c r="L151" s="9"/>
+      <c r="M151" s="9"/>
+      <c r="N151" s="9"/>
+      <c r="O151" s="9"/>
+      <c r="P151" s="9"/>
+      <c r="Q151" s="9"/>
+      <c r="R151" s="9"/>
+      <c r="S151" s="9"/>
+      <c r="T151" s="9"/>
+      <c r="U151" s="9"/>
+      <c r="V151" s="9"/>
+      <c r="W151" s="9"/>
+      <c r="X151" s="9"/>
+      <c r="Y151" s="9"/>
+      <c r="Z151" s="9"/>
+      <c r="AA151" s="9"/>
+      <c r="AB151" s="9"/>
+      <c r="AC151" s="9"/>
+      <c r="AD151" s="9"/>
+      <c r="AE151" s="9"/>
+      <c r="AF151" s="9"/>
+      <c r="AG151" s="9"/>
+      <c r="AH151" s="9"/>
+    </row>
+    <row r="152" spans="1:34" ht="16.2" thickBot="1">
+      <c r="A152" s="8">
+        <v>150</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C152" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="153" spans="1:34" ht="16.2" thickBot="1">
+      <c r="C153" s="9"/>
+    </row>
+    <row r="154" spans="1:34" ht="16.2" thickBot="1">
+      <c r="C154" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
